--- a/TESTER/Bài tập.xlsx
+++ b/TESTER/Bài tập.xlsx
@@ -8,29 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTER\DangVanKhoa\TESTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74D550D-E46A-4689-903C-78EAA977222E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE87282-5028-4D1A-A932-17251153024C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="17" xr2:uid="{B04854CF-6AF7-4D59-B8A6-A60630F930F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{B04854CF-6AF7-4D59-B8A6-A60630F930F7}"/>
   </bookViews>
   <sheets>
-    <sheet name="LAB 1 Bài 1" sheetId="1" r:id="rId1"/>
-    <sheet name="LAB 1 Bài 2" sheetId="4" r:id="rId2"/>
-    <sheet name="LAB 1 Bài 3" sheetId="5" r:id="rId3"/>
-    <sheet name="LAB 1 Bài 4" sheetId="6" r:id="rId4"/>
-    <sheet name="LAB 1 Bài 5" sheetId="7" r:id="rId5"/>
-    <sheet name="LAB 1 Bài 6" sheetId="8" r:id="rId6"/>
-    <sheet name="LAB 2 Bài 1" sheetId="9" r:id="rId7"/>
-    <sheet name="LAB 2 Bài 2" sheetId="10" r:id="rId8"/>
-    <sheet name="LAB 2 Bài 3" sheetId="11" r:id="rId9"/>
-    <sheet name="LAB 2 Bài 4" sheetId="12" r:id="rId10"/>
-    <sheet name="LAB 2 Bài 5" sheetId="13" r:id="rId11"/>
-    <sheet name="LAB 2 Bài 6" sheetId="14" r:id="rId12"/>
-    <sheet name="LAB 2 Bài 7" sheetId="15" r:id="rId13"/>
-    <sheet name="LAB 2 Bài 8" sheetId="16" r:id="rId14"/>
-    <sheet name="LAB 3 Bài 1" sheetId="18" r:id="rId15"/>
-    <sheet name="LAB 3 Bài 2" sheetId="19" r:id="rId16"/>
-    <sheet name="LAB 3 Bài 3" sheetId="20" r:id="rId17"/>
-    <sheet name="LAB 3 Bài 4" sheetId="21" r:id="rId18"/>
+    <sheet name="Tuần 1 Bài 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tuần 1 Bài 2" sheetId="4" r:id="rId2"/>
+    <sheet name="Tuần 1 Bài 3" sheetId="5" r:id="rId3"/>
+    <sheet name="Tuần 1 Bài 4" sheetId="6" r:id="rId4"/>
+    <sheet name="Tuần 1 Bài 5" sheetId="7" r:id="rId5"/>
+    <sheet name="Tuần 1 Bài 6" sheetId="8" r:id="rId6"/>
+    <sheet name="Tuần 2 LAB 2 Bài 1" sheetId="9" r:id="rId7"/>
+    <sheet name="Tuần 2 LAB 2 Bài 2" sheetId="10" r:id="rId8"/>
+    <sheet name="Tuần 2 LAB 2 Bài 3" sheetId="11" r:id="rId9"/>
+    <sheet name="Tuần 2 LAB 2 Bài 4" sheetId="12" r:id="rId10"/>
+    <sheet name="Tuần 2 LAB 2 Bài 5" sheetId="13" r:id="rId11"/>
+    <sheet name="Tuần 2 LAB 2 Bài 6" sheetId="14" r:id="rId12"/>
+    <sheet name="Tuần 2 LAB 2 Bài 7" sheetId="15" r:id="rId13"/>
+    <sheet name="Tuần 2 LAB 2 Bài 8" sheetId="16" r:id="rId14"/>
+    <sheet name="Tuần 2 LAB 3 Bài 1" sheetId="18" r:id="rId15"/>
+    <sheet name="Tuần 2 LAB 3 Bài 2" sheetId="19" r:id="rId16"/>
+    <sheet name="Tuần 2 LAB 3 Bài 3" sheetId="20" r:id="rId17"/>
+    <sheet name="Tuần 2 LAB 3 Bài 4" sheetId="21" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2318,24 +2318,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2386,9 +2368,6 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2404,6 +2383,27 @@
     </xf>
     <xf numFmtId="6" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2846,10 +2846,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2900,12 +2900,12 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
@@ -2980,12 +2980,12 @@
       <c r="E13" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
     </row>
     <row r="16" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
@@ -4305,882 +4305,882 @@
   <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" style="31" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="31"/>
+    <col min="1" max="1" width="20.33203125" style="25" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="54" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="48" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="54" t="s">
         <v>421</v>
       </c>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
     </row>
     <row r="2" spans="1:10" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="42" t="s">
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="36" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="117.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="29" t="s">
         <v>415</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="29" t="s">
         <v>423</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="117.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="29" t="s">
         <v>424</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="29" t="s">
         <v>425</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="29" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="117.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="29" t="s">
         <v>426</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="29" t="s">
         <v>418</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="29" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="29" t="s">
         <v>418</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="29" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="24" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="27" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="25" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="26" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="26" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="26" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="27" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="26" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="26" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="26" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="26" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="25" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
+      <c r="A21" s="27"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="24" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="25" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="25" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="24" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="36" t="s">
         <v>437</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="37" t="s">
         <v>438</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="37" t="s">
         <v>439</v>
       </c>
-      <c r="D27" s="43" t="s">
+      <c r="D27" s="37" t="s">
         <v>440</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="E27" s="37" t="s">
         <v>441</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="G27" s="43" t="s">
+      <c r="G27" s="37" t="s">
         <v>443</v>
       </c>
-      <c r="H27" s="43" t="s">
+      <c r="H27" s="37" t="s">
         <v>444</v>
       </c>
-      <c r="I27" s="43" t="s">
+      <c r="I27" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="J27" s="43" t="s">
+      <c r="J27" s="37" t="s">
         <v>447</v>
       </c>
-      <c r="K27" s="43" t="s">
+      <c r="K27" s="37" t="s">
         <v>448</v>
       </c>
-      <c r="L27" s="43" t="s">
+      <c r="L27" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="M27" s="43" t="s">
+      <c r="M27" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="N27" s="43" t="s">
+      <c r="N27" s="37" t="s">
         <v>451</v>
       </c>
-      <c r="O27" s="43" t="s">
+      <c r="O27" s="37" t="s">
         <v>452</v>
       </c>
-      <c r="P27" s="43" t="s">
+      <c r="P27" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="Q27" s="43" t="s">
+      <c r="Q27" s="37" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="38" t="s">
         <v>459</v>
       </c>
-      <c r="B28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="I28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="J28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="K28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="L28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="M28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="N28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="O28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q28" s="45" t="s">
+      <c r="B28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="H28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="I28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="J28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="K28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="L28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="M28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="N28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="O28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="P28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q28" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="38" t="s">
         <v>460</v>
       </c>
-      <c r="B29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="F29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="G29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="I29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="K29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="L29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="M29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="N29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="O29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="P29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q29" s="45" t="s">
+      <c r="B29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="K29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="L29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="M29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="N29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="O29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="P29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q29" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="38" t="s">
         <v>461</v>
       </c>
-      <c r="B30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="H30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="I30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="K30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="L30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="M30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="N30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="O30" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="P30" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q30" s="45" t="s">
+      <c r="B30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="K30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="L30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="M30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="N30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="O30" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="P30" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q30" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="38" t="s">
         <v>462</v>
       </c>
-      <c r="B31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="H31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="I31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="K31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="L31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="M31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="N31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="O31" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="P31" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q31" s="45" t="s">
+      <c r="B31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="K31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="L31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="M31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="N31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="O31" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="P31" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q31" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="38" t="s">
         <v>412</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
     </row>
     <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="42"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
     </row>
     <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="38" t="s">
         <v>455</v>
       </c>
-      <c r="B35" s="45" t="s">
+      <c r="B35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="C35" s="45" t="s">
+      <c r="C35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="D35" s="45" t="s">
+      <c r="D35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="E35" s="45" t="s">
+      <c r="E35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="F35" s="45" t="s">
+      <c r="F35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="H35" s="45" t="s">
+      <c r="H35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="I35" s="45" t="s">
+      <c r="I35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45" t="s">
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="Q35" s="45" t="s">
+      <c r="Q35" s="39" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="44" t="s">
+      <c r="A36" s="38" t="s">
         <v>457</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45" t="s">
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="O36" s="45" t="s">
+      <c r="O36" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="44" t="s">
+      <c r="A37" s="38" t="s">
         <v>458</v>
       </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45" t="s">
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="44" t="s">
+      <c r="A38" s="38" t="s">
         <v>463</v>
       </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45" t="s">
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45" t="s">
+      <c r="L38" s="39"/>
+      <c r="M38" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="45"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="38" t="s">
         <v>464</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45" t="s">
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39" t="s">
         <v>456</v>
       </c>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
     </row>
     <row r="41" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="24" t="s">
         <v>476</v>
       </c>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="27" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="42" t="s">
+      <c r="A43" s="36" t="s">
         <v>481</v>
       </c>
-      <c r="B43" s="43" t="s">
+      <c r="B43" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="C43" s="43" t="s">
+      <c r="C43" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="D43" s="43" t="s">
+      <c r="D43" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="E43" s="43" t="s">
+      <c r="E43" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="F43" s="43" t="s">
+      <c r="F43" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="G43" s="43" t="s">
+      <c r="G43" s="37" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="44" t="s">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="38" t="s">
         <v>471</v>
       </c>
-      <c r="B44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="G44" s="45" t="s">
+      <c r="B44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="G44" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="44" t="s">
+      <c r="A45" s="38" t="s">
         <v>472</v>
       </c>
-      <c r="B45" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D45" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E45" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F45" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G45" s="45" t="s">
+      <c r="B45" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G45" s="39" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="38" t="s">
         <v>474</v>
       </c>
-      <c r="B46" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D46" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E46" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F46" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G46" s="45" t="s">
+      <c r="B46" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F46" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G46" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
+      <c r="A47" s="38" t="s">
         <v>475</v>
       </c>
-      <c r="B47" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D47" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E47" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F47" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G47" s="45" t="s">
+      <c r="B47" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F47" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G47" s="39" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="44"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
+      <c r="A48" s="38"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="44" t="s">
+      <c r="A49" s="38" t="s">
         <v>412</v>
       </c>
-      <c r="B49" s="35"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="44" t="s">
+      <c r="A50" s="38" t="s">
         <v>455</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35" t="s">
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="44" t="s">
+      <c r="A51" s="38" t="s">
         <v>457</v>
       </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="44" t="s">
+      <c r="A52" s="38" t="s">
         <v>458</v>
       </c>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35" t="s">
+      <c r="B52" s="29"/>
+      <c r="C52" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="G52" s="41" t="s">
+      <c r="E52" s="29"/>
+      <c r="G52" s="35" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="38" t="s">
         <v>463</v>
       </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35" t="s">
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="44" t="s">
+      <c r="A54" s="38" t="s">
         <v>464</v>
       </c>
-      <c r="F54" s="41" t="s">
+      <c r="F54" s="35" t="s">
         <v>413</v>
       </c>
     </row>
@@ -5200,28 +5200,763 @@
   <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="31" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="31"/>
+    <col min="1" max="1" width="14.33203125" style="25" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="42" t="s">
         <v>507</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="49"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="42"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
-      <c r="K1" s="49"/>
+      <c r="K1" s="42"/>
       <c r="L1"/>
       <c r="M1"/>
       <c r="N1"/>
     </row>
     <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="32"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+    </row>
+    <row r="3" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="31"/>
+    </row>
+    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+    </row>
+    <row r="5" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>512</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+    </row>
+    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>515</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
+        <v>491</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="H27" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="H28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="39"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="38" t="s">
+        <v>493</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="39"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="38" t="s">
+        <v>494</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
+        <v>495</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="39"/>
+    </row>
+    <row r="33" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="39"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="39"/>
+      <c r="P33" s="39"/>
+      <c r="Q33" s="39"/>
+    </row>
+    <row r="34" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="38" t="s">
+        <v>497</v>
+      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="J34" s="39"/>
+      <c r="K34" s="39"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="39"/>
+      <c r="P34" s="39"/>
+      <c r="Q34" s="39"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A35" s="38" t="s">
+        <v>476</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="39"/>
+      <c r="P35" s="39"/>
+      <c r="Q35" s="39"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="39"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A38" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="39"/>
+      <c r="P38" s="39"/>
+      <c r="Q38" s="39"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="26" t="s">
+        <v>505</v>
+      </c>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A40" s="25" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A41" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A43" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A44" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="38" t="s">
+        <v>494</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>456</v>
+      </c>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="38" t="s">
+        <v>495</v>
+      </c>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="38" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="38" t="s">
+        <v>497</v>
+      </c>
+      <c r="B48" s="39"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="38"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="38"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="38"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="38"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="G52" s="35"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="38"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="38"/>
+      <c r="F54" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E5DDFC-B5C5-4218-B3E3-729F6135F673}">
+  <dimension ref="A1:S49"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="25" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
         <v>34</v>
       </c>
@@ -5229,462 +5964,612 @@
         <v>506</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>36</v>
+        <v>519</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-    </row>
-    <row r="3" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="F2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="P2" s="24"/>
+    </row>
+    <row r="3" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>508</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>509</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="37"/>
-    </row>
-    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="B3" s="29" t="s">
+        <v>547</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>533</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="37" t="s">
-        <v>510</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>511</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-    </row>
-    <row r="5" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="B4" s="29" t="s">
+        <v>548</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>520</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+    </row>
+    <row r="5" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="37" t="s">
-        <v>512</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>513</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-    </row>
-    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="B5" s="29" t="s">
+        <v>549</v>
+      </c>
+      <c r="C5" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+    </row>
+    <row r="6" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
         <v>514</v>
       </c>
-      <c r="B6" s="37" t="s">
-        <v>515</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>516</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>517</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>418</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
-        <v>485</v>
+      <c r="B6" s="29" t="s">
+        <v>550</v>
+      </c>
+      <c r="C6" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+    </row>
+    <row r="7" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
+        <v>521</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>551</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>522</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="32" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="44" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="32" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="32" t="s">
-        <v>482</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="32" t="s">
-        <v>483</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="32" t="s">
-        <v>484</v>
+        <v>541</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
+      <c r="A21" s="32" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
-        <v>407</v>
+      <c r="A22" s="25" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
-        <v>408</v>
+      <c r="A24" s="32" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="42" t="s">
-        <v>490</v>
-      </c>
-      <c r="B26" s="43" t="s">
+      <c r="A26" s="46" t="s">
+        <v>409</v>
+      </c>
+      <c r="B26" s="36" t="s">
         <v>438</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="36" t="s">
         <v>439</v>
       </c>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="36" t="s">
         <v>440</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="G26" s="43" t="s">
+      <c r="G26" s="36" t="s">
         <v>443</v>
       </c>
-      <c r="H26" s="43" t="s">
+      <c r="H26" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="I26" s="43" t="s">
+      <c r="I26" s="36" t="s">
         <v>445</v>
       </c>
+      <c r="J26" s="36" t="s">
+        <v>447</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="L26" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="M26" s="36" t="s">
+        <v>450</v>
+      </c>
+      <c r="N26" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="O26" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="P26" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q26" s="36" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
-        <v>491</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D27" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="F27" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="G27" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="I27" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
+      <c r="A27" s="38" t="s">
+        <v>543</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="O27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q27" s="28" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
-        <v>492</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G28" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="H28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="I28" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="M28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="N28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="O28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q28" s="28" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
-        <v>493</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="H29" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="I29" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="38" t="s">
+        <v>544</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="L29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="M29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="O29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="P29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q29" s="28" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="M30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="O30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q30" s="28" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="44" t="s">
-        <v>494</v>
-      </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A32" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="B32" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="45"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
-        <v>495</v>
-      </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45" t="s">
-        <v>456</v>
-      </c>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-    </row>
-    <row r="33" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
-        <v>496</v>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A33" s="38" t="s">
+        <v>528</v>
       </c>
       <c r="B33" s="45"/>
       <c r="C33" s="45"/>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E33" s="45"/>
+      <c r="E33" s="28" t="s">
+        <v>456</v>
+      </c>
       <c r="F33" s="45"/>
       <c r="G33" s="45"/>
-      <c r="H33" s="45" t="s">
+      <c r="H33" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="I33" s="45"/>
+      <c r="I33" s="28" t="s">
+        <v>456</v>
+      </c>
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
+      <c r="L33" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>456</v>
+      </c>
       <c r="N33" s="45"/>
       <c r="O33" s="45"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
-    </row>
-    <row r="34" spans="1:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
-        <v>497</v>
+      <c r="P33" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q33" s="28" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="38" t="s">
+        <v>529</v>
       </c>
       <c r="B34" s="45"/>
-      <c r="C34" s="45" t="s">
-        <v>456</v>
-      </c>
+      <c r="C34" s="45"/>
       <c r="D34" s="45"/>
-      <c r="E34" s="45" t="s">
-        <v>456</v>
-      </c>
+      <c r="E34" s="45"/>
       <c r="F34" s="45"/>
-      <c r="G34" s="45" t="s">
-        <v>456</v>
-      </c>
+      <c r="G34" s="45"/>
       <c r="H34" s="45"/>
-      <c r="I34" s="45" t="s">
-        <v>456</v>
-      </c>
+      <c r="I34" s="45"/>
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
       <c r="L34" s="45"/>
       <c r="M34" s="45"/>
-      <c r="N34" s="45"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
+      <c r="N34" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="O34" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="P34" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q34" s="28" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
-        <v>476</v>
+      <c r="A35" s="38" t="s">
+        <v>530</v>
       </c>
       <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
+      <c r="C35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
+      <c r="E35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="G35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
+      <c r="I35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
+      <c r="K35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
+      <c r="M35" s="45" t="s">
+        <v>456</v>
+      </c>
       <c r="N35" s="45"/>
       <c r="O35" s="45"/>
       <c r="P35" s="45"/>
       <c r="Q35" s="45"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="32" t="s">
-        <v>502</v>
-      </c>
       <c r="B36" s="45"/>
       <c r="C36" s="45"/>
       <c r="D36" s="45"/>
@@ -5704,1064 +6589,179 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
-        <v>503</v>
-      </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
+        <v>531</v>
+      </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="32" t="s">
-        <v>504</v>
-      </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="45"/>
-      <c r="Q38" s="45"/>
+      <c r="A38" s="26" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="32" t="s">
-        <v>505</v>
-      </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="45"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="45"/>
-      <c r="Q39" s="45"/>
+      <c r="A39" s="26"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="31" t="s">
-        <v>498</v>
+      <c r="A40" s="36" t="s">
+        <v>532</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>438</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="42" t="s">
-        <v>409</v>
-      </c>
-      <c r="B41" s="43" t="s">
-        <v>438</v>
-      </c>
-      <c r="C41" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="D41" s="43" t="s">
-        <v>440</v>
-      </c>
-      <c r="E41" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
+      <c r="A41" s="38" t="s">
+        <v>459</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="35" t="s">
-        <v>499</v>
-      </c>
-      <c r="B42" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="D42" s="45" t="s">
-        <v>473</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>473</v>
+      <c r="A42" s="38" t="s">
+        <v>545</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
-        <v>500</v>
-      </c>
-      <c r="B43" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C43" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D43" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E43" s="45" t="s">
-        <v>473</v>
-      </c>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="35" t="s">
-        <v>501</v>
-      </c>
-      <c r="B44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="E44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
+      <c r="A43" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="44" t="s">
-        <v>494</v>
-      </c>
-      <c r="B45" s="46" t="s">
+      <c r="A45" s="46" t="s">
+        <v>412</v>
+      </c>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="B46" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
-        <v>495</v>
-      </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45" t="s">
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="38" t="s">
+        <v>528</v>
+      </c>
+      <c r="B47" s="45"/>
+      <c r="C47" s="45" t="s">
         <v>456</v>
       </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
-        <v>496</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="45"/>
+      <c r="E47" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E47" s="45"/>
       <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
+      <c r="G47" s="45" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="44" t="s">
-        <v>497</v>
+      <c r="A48" s="38" t="s">
+        <v>529</v>
       </c>
       <c r="B48" s="45"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="45" t="s">
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45" t="s">
         <v>456</v>
       </c>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
+      <c r="G48" s="45" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="44"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="44"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="44"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="44"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="G52" s="41"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="44"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="44"/>
-      <c r="F54" s="41"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E5DDFC-B5C5-4218-B3E3-729F6135F673}">
-  <dimension ref="A1:S49"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.44140625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="31" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="31"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>506</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>519</v>
-      </c>
-      <c r="D2" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="P2" s="30"/>
-    </row>
-    <row r="3" spans="1:19" ht="84" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>547</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="84" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>548</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>520</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-    </row>
-    <row r="5" spans="1:19" ht="84" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>549</v>
-      </c>
-      <c r="C5" s="50">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-    </row>
-    <row r="6" spans="1:19" ht="84" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>514</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>550</v>
-      </c>
-      <c r="C6" s="50">
-        <v>0.1</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-    </row>
-    <row r="7" spans="1:19" ht="84" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>521</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>551</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>522</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="38" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="38" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="38" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="38" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="31" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="38" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="53" t="s">
-        <v>409</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>439</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>440</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>441</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="G26" s="42" t="s">
-        <v>443</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="I26" s="42" t="s">
-        <v>445</v>
-      </c>
-      <c r="J26" s="42" t="s">
-        <v>447</v>
-      </c>
-      <c r="K26" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="L26" s="42" t="s">
-        <v>449</v>
-      </c>
-      <c r="M26" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="N26" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="O26" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="P26" s="42" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q26" s="42" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
-        <v>543</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="J27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="K27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="L27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="M27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="O27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q27" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
-        <v>460</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="L28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="M28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="N28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="O28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q28" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
-        <v>544</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="L29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="P29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q29" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
-        <v>462</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="I30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="L30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="M30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="O30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q30" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
-        <v>527</v>
-      </c>
-      <c r="B32" s="34" t="s">
+      <c r="A49" s="38" t="s">
+        <v>530</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
-        <v>528</v>
-      </c>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="34" t="s">
+      <c r="E49" s="45" t="s">
         <v>456</v>
       </c>
-      <c r="E33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="M33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="N33" s="52"/>
-      <c r="O33" s="52"/>
-      <c r="P33" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q33" s="34" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
-        <v>529</v>
-      </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="O34" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="P34" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q34" s="34" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
-        <v>530</v>
-      </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="38" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="32" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="32"/>
-    </row>
-    <row r="40" spans="1:17" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="42" t="s">
-        <v>532</v>
-      </c>
-      <c r="B40" s="43" t="s">
-        <v>438</v>
-      </c>
-      <c r="C40" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>440</v>
-      </c>
-      <c r="E40" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="F40" s="43" t="s">
-        <v>442</v>
-      </c>
-      <c r="G40" s="43" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="44" t="s">
-        <v>459</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E41" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="F41" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="G41" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="44" t="s">
-        <v>545</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F42" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G42" s="34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="44" t="s">
-        <v>461</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="E43" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F43" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G43" s="34" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
-        <v>527</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
-        <v>528</v>
-      </c>
-      <c r="B47" s="52"/>
-      <c r="C47" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="D47" s="52"/>
-      <c r="E47" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="44" t="s">
-        <v>529</v>
-      </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="G48" s="52" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="44" t="s">
-        <v>530</v>
-      </c>
-      <c r="B49" s="52"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="34" t="s">
-        <v>456</v>
-      </c>
-      <c r="E49" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="F49" s="52"/>
-      <c r="G49" s="52"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6773,748 +6773,748 @@
   <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.88671875" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.88671875" style="31" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="31" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="31" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="31"/>
+    <col min="1" max="1" width="30.88671875" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.88671875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="25" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="25" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="28" t="s">
         <v>552</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="29" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="29" t="s">
         <v>514</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="29" t="s">
         <v>561</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="29" t="s">
         <v>555</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="29" t="s">
         <v>563</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="29" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="24" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="25" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="25" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="25" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="25" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="25" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="25" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="25" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="25" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="25" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="32" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="25" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="32" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="36" t="s">
         <v>409</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="36" t="s">
         <v>438</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="36" t="s">
         <v>439</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="36" t="s">
         <v>440</v>
       </c>
-      <c r="E26" s="42" t="s">
+      <c r="E26" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="36" t="s">
         <v>443</v>
       </c>
-      <c r="H26" s="42" t="s">
+      <c r="H26" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="I26" s="42" t="s">
+      <c r="I26" s="36" t="s">
         <v>445</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="J26" s="36" t="s">
         <v>447</v>
       </c>
-      <c r="K26" s="42" t="s">
+      <c r="K26" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="L26" s="42" t="s">
+      <c r="L26" s="36" t="s">
         <v>449</v>
       </c>
-      <c r="M26" s="42" t="s">
+      <c r="M26" s="36" t="s">
         <v>450</v>
       </c>
-      <c r="N26" s="42" t="s">
+      <c r="N26" s="36" t="s">
         <v>451</v>
       </c>
-      <c r="O26" s="42" t="s">
+      <c r="O26" s="36" t="s">
         <v>452</v>
       </c>
-      <c r="P26" s="42" t="s">
+      <c r="P26" s="36" t="s">
         <v>453</v>
       </c>
-      <c r="Q26" s="42" t="s">
+      <c r="Q26" s="36" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="38" t="s">
         <v>568</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="J27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="K27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="L27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="M27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="O27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P27" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q27" s="34" t="s">
+      <c r="B27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="M27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="O27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P27" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q27" s="28" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="38" t="s">
         <v>569</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="L28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="M28" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="N28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="O28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P28" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q28" s="34" t="s">
+      <c r="B28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="M28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="N28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="O28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q28" s="28" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="38" t="s">
         <v>446</v>
       </c>
-      <c r="B29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="L29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="P29" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q29" s="34" t="s">
+      <c r="B29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="L29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="M29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="O29" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="P29" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q29" s="28" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="38" t="s">
         <v>570</v>
       </c>
-      <c r="B30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="I30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="J30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="K30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="L30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="M30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="N30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="O30" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P30" s="34" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q30" s="34" t="s">
+      <c r="B30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="I30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="K30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="M30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="O30" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="P30" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q30" s="28" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="36" t="s">
         <v>412</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="38" t="s">
         <v>571</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34" t="s">
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="O32" s="34" t="s">
+      <c r="O32" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="P32" s="34" t="s">
+      <c r="P32" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="Q32" s="34" t="s">
+      <c r="Q32" s="28" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="38" t="s">
         <v>572</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34" t="s">
+      <c r="B33" s="28"/>
+      <c r="C33" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34" t="s">
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
+      <c r="A34" s="38" t="s">
         <v>573</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34" t="s">
+      <c r="C34" s="28"/>
+      <c r="D34" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34" t="s">
+      <c r="E34" s="28"/>
+      <c r="F34" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G34" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="32" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="25" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="25" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="25" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="25" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="42" t="s">
+      <c r="A41" s="36" t="s">
         <v>577</v>
       </c>
-      <c r="B41" s="43" t="s">
+      <c r="B41" s="37" t="s">
         <v>438</v>
       </c>
-      <c r="C41" s="43" t="s">
+      <c r="C41" s="37" t="s">
         <v>439</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D41" s="37" t="s">
         <v>440</v>
       </c>
-      <c r="E41" s="43" t="s">
+      <c r="E41" s="37" t="s">
         <v>441</v>
       </c>
-      <c r="F41" s="43" t="s">
+      <c r="F41" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="G41" s="43" t="s">
+      <c r="G41" s="37" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="39" t="s">
         <v>579</v>
       </c>
-      <c r="C42" s="45" t="s">
+      <c r="C42" s="39" t="s">
         <v>580</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" s="39" t="s">
         <v>580</v>
       </c>
-      <c r="E42" s="45" t="s">
+      <c r="E42" s="39" t="s">
         <v>581</v>
       </c>
-      <c r="F42" s="45" t="s">
+      <c r="F42" s="39" t="s">
         <v>581</v>
       </c>
-      <c r="G42" s="45" t="s">
+      <c r="G42" s="39" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="35" t="s">
+      <c r="A43" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="B43" s="45" t="s">
+      <c r="B43" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="E43" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="F43" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="G43" s="45" t="s">
+      <c r="E43" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="G43" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="B44" s="45" t="s">
+      <c r="B44" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="C44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="D44" s="45" t="s">
-        <v>411</v>
-      </c>
-      <c r="E44" s="45" t="s">
+      <c r="C44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="E44" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="F44" s="45" t="s">
-        <v>410</v>
-      </c>
-      <c r="G44" s="45" t="s">
+      <c r="F44" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="G44" s="39" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="36" t="s">
         <v>412</v>
       </c>
-      <c r="B45" s="54">
+      <c r="B45" s="47">
         <v>0</v>
       </c>
-      <c r="C45" s="54">
+      <c r="C45" s="47">
         <v>10</v>
       </c>
-      <c r="D45" s="54">
+      <c r="D45" s="47">
         <v>5</v>
       </c>
-      <c r="E45" s="54">
+      <c r="E45" s="47">
         <v>10</v>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="47">
         <v>5</v>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="47">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="38" t="s">
         <v>571</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34" t="s">
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
+      <c r="A47" s="38" t="s">
         <v>572</v>
       </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34" t="s">
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34" t="s">
+      <c r="E47" s="28"/>
+      <c r="F47" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="G47" s="34"/>
+      <c r="G47" s="28"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="44" t="s">
+      <c r="A48" s="38" t="s">
         <v>573</v>
       </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34" t="s">
+      <c r="B48" s="28"/>
+      <c r="C48" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34" t="s">
+      <c r="D48" s="28"/>
+      <c r="E48" s="28" t="s">
         <v>456</v>
       </c>
     </row>
@@ -7545,10 +7545,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -7627,13 +7627,13 @@
       <c r="E7" s="13"/>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
@@ -7704,12 +7704,12 @@
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7862,10 +7862,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -7937,13 +7937,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
@@ -8014,12 +8014,12 @@
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8172,10 +8172,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -8247,13 +8247,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
@@ -8361,13 +8361,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
@@ -8536,10 +8536,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -8611,12 +8611,12 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8698,12 +8698,12 @@
       <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="29"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8891,10 +8891,10 @@
       <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="24"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -8966,12 +8966,12 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
       <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,12 +9083,12 @@
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="29"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="53"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">

--- a/TESTER/Bài tập.xlsx
+++ b/TESTER/Bài tập.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTER\DangVanKhoa\TESTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE87282-5028-4D1A-A932-17251153024C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B038A5E-FBF1-4FCB-A86E-29EAE9065743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="17" xr2:uid="{B04854CF-6AF7-4D59-B8A6-A60630F930F7}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="589">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -2071,6 +2071,9 @@
   </si>
   <si>
     <t>A10: Ship = $10</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -6770,7 +6773,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46FA079-7733-4056-A284-F1887C5B37D8}">
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q146"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.88671875" style="25" bestFit="1" customWidth="1"/>
@@ -7516,6 +7519,11 @@
       <c r="D48" s="28"/>
       <c r="E48" s="28" t="s">
         <v>456</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B146" s="25" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>
